--- a/outputs/42930.xlsx
+++ b/outputs/42930.xlsx
@@ -131,8 +131,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -328,321 +332,321 @@
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1910</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <f aca="false">MATCH(B2,$E$2:$E$8,0)</f>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B2,$E$2:$E$8,0))</f>
         <v>1</v>
       </c>
-      <c r="E2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="0" t="n">
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>1910</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <f aca="false">MATCH(B3,$E$2:$E$8,0)</f>
+      <c r="C3" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B3,$E$2:$E$8,0))</f>
         <v>2</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>1911</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <f aca="false">MATCH(B4,$E$2:$E$8,0)</f>
+      <c r="C4" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B4,$E$2:$E$8,0))</f>
         <v>3</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>1912</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <f aca="false">MATCH(B5,$E$2:$E$8,0)</f>
+      <c r="C5" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B5,$E$2:$E$8,0))</f>
         <v>4</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>1913</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <f aca="false">MATCH(B6,$E$2:$E$8,0)</f>
-        <v>5</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="C6" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B6,$E$2:$E$8,0))</f>
+        <v>5</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>1913</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <f aca="false">MATCH(B7,$E$2:$E$8,0)</f>
-        <v>5</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="C7" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B7,$E$2:$E$8,0))</f>
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>1913</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <f aca="false">MATCH(B8,$E$2:$E$8,0)</f>
+      <c r="C8" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B8,$E$2:$E$8,0))</f>
         <v>2</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>1914</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <f aca="false">MATCH(B9,$E$2:$E$8,0)</f>
+      <c r="C9" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B9,$E$2:$E$8,0))</f>
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>1914</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="0" t="n">
-        <f aca="false">MATCH(B10,$E$2:$E$8,0)</f>
+      <c r="C10" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B10,$E$2:$E$8,0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>1915</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="0" t="n">
-        <f aca="false">MATCH(B11,$E$2:$E$8,0)</f>
+      <c r="C11" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B11,$E$2:$E$8,0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>1916</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="0" t="n">
-        <f aca="false">MATCH(B12,$E$2:$E$8,0)</f>
+      <c r="C12" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B12,$E$2:$E$8,0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>1917</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="0" t="n">
-        <f aca="false">MATCH(B13,$E$2:$E$8,0)</f>
+      <c r="C13" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B13,$E$2:$E$8,0))</f>
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>1918</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="0" t="n">
-        <f aca="false">MATCH(B14,$E$2:$E$8,0)</f>
+      <c r="C14" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B14,$E$2:$E$8,0))</f>
         <v>7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>1918</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="0" t="n">
-        <f aca="false">MATCH(B15,$E$2:$E$8,0)</f>
+      <c r="C15" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B15,$E$2:$E$8,0))</f>
         <v>7</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>1918</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="0" t="n">
-        <f aca="false">MATCH(B16,$E$2:$E$8,0)</f>
+      <c r="C16" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B16,$E$2:$E$8,0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>1919</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="0" t="n">
-        <f aca="false">MATCH(B17,$E$2:$E$8,0)</f>
+      <c r="C17" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B17,$E$2:$E$8,0))</f>
         <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>1919</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="0" t="n">
-        <f aca="false">MATCH(B18,$E$2:$E$8,0)</f>
+      <c r="C18" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B18,$E$2:$E$8,0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>1920</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="0" t="n">
-        <f aca="false">MATCH(B19,$E$2:$E$8,0)</f>
+      <c r="C19" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B19,$E$2:$E$8,0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>1920</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="0" t="n">
-        <f aca="false">MATCH(B20,$E$2:$E$8,0)</f>
+      <c r="B20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B20,$E$2:$E$8,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>1921</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="0" t="n">
-        <f aca="false">MATCH(B21,$E$2:$E$8,0)</f>
+      <c r="B21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B21,$E$2:$E$8,0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>1921</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <f aca="false">MATCH(B22,$E$2:$E$8,0)</f>
+      <c r="B22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <f aca="false">INDEX($F$2:$F$8,MATCH(B22,$E$2:$E$8,0))</f>
         <v>1</v>
       </c>
     </row>

--- a/outputs/42930.xlsx
+++ b/outputs/42930.xlsx
@@ -339,7 +339,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30.29"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -356,7 +356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1910</v>
       </c>
@@ -364,7 +364,6 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B2,$E$2:$E$8,0))</f>
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -374,7 +373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1910</v>
       </c>
@@ -382,7 +381,6 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B3,$E$2:$E$8,0))</f>
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -392,7 +390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1911</v>
       </c>
@@ -400,7 +398,6 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B4,$E$2:$E$8,0))</f>
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -410,7 +407,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>1912</v>
       </c>
@@ -418,7 +415,6 @@
         <v>8</v>
       </c>
       <c r="C5" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B5,$E$2:$E$8,0))</f>
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -428,7 +424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>1913</v>
       </c>
@@ -436,7 +432,6 @@
         <v>9</v>
       </c>
       <c r="C6" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B6,$E$2:$E$8,0))</f>
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -446,7 +441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>1913</v>
       </c>
@@ -454,7 +449,6 @@
         <v>9</v>
       </c>
       <c r="C7" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B7,$E$2:$E$8,0))</f>
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -464,7 +458,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>1913</v>
       </c>
@@ -472,7 +466,6 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B8,$E$2:$E$8,0))</f>
         <v>2</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -482,7 +475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>1914</v>
       </c>
@@ -490,11 +483,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B9,$E$2:$E$8,0))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>1914</v>
       </c>
@@ -502,11 +494,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B10,$E$2:$E$8,0))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>1915</v>
       </c>
@@ -514,11 +505,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B11,$E$2:$E$8,0))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>1916</v>
       </c>
@@ -526,11 +516,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B12,$E$2:$E$8,0))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>1917</v>
       </c>
@@ -538,11 +527,10 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B13,$E$2:$E$8,0))</f>
         <v>6</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>1918</v>
       </c>
@@ -550,11 +538,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B14,$E$2:$E$8,0))</f>
         <v>7</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>1918</v>
       </c>
@@ -562,11 +549,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B15,$E$2:$E$8,0))</f>
         <v>7</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>1918</v>
       </c>
@@ -574,11 +560,10 @@
         <v>9</v>
       </c>
       <c r="C16" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B16,$E$2:$E$8,0))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>1919</v>
       </c>
@@ -586,11 +571,10 @@
         <v>8</v>
       </c>
       <c r="C17" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B17,$E$2:$E$8,0))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>1919</v>
       </c>
@@ -598,11 +582,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B18,$E$2:$E$8,0))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>1920</v>
       </c>
@@ -610,11 +593,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B19,$E$2:$E$8,0))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>1920</v>
       </c>
@@ -622,11 +604,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B20,$E$2:$E$8,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>1921</v>
       </c>
@@ -634,11 +615,10 @@
         <v>5</v>
       </c>
       <c r="C21" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B21,$E$2:$E$8,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>1921</v>
       </c>
@@ -646,7 +626,6 @@
         <v>5</v>
       </c>
       <c r="C22" s="1" t="n">
-        <f aca="false">INDEX($F$2:$F$8,MATCH(B22,$E$2:$E$8,0))</f>
         <v>1</v>
       </c>
     </row>
